--- a/docs/ejemplos/creditos-reportes/vacio.xlsx
+++ b/docs/ejemplos/creditos-reportes/vacio.xlsx
@@ -9,15 +9,15 @@
     <sheet sheetId="3" name="Cuotas y pagos" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumen'!$13:$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Créditos'!$13:$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumen'!$15:$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Créditos'!$15:$15</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="69">
   <si>
     <t>Créditos · Consolidado Grupo Mediterra</t>
   </si>
@@ -43,6 +43,12 @@
     <t>sin rango · todas las cuotas y pagos</t>
   </si>
   <si>
+    <t>Cómo leer</t>
+  </si>
+  <si>
+    <t>La fecha de corte determina los SALDOS (capital, sin desglose, intereses, vencido, por conciliar, pagado) de toda la cartera filtrada. El rango solo filtra los MOVIMIENTOS listados (cuotas por vencimiento, pagos por fecha efectiva) y no cambia ningún saldo. Los totales marcados «cartera al corte» incluyen todo el crédito; los marcados «solo filas del rango», únicamente las filas listadas.</t>
+  </si>
+  <si>
     <t>Empresa (deudora)</t>
   </si>
   <si>
@@ -70,6 +76,9 @@
     <t>todos · solo pagos vigentes (los anulados no se listan)</t>
   </si>
   <si>
+    <t>Resumen · saldos al corte de toda la cartera filtrada (cartera al corte; el rango no los cambia)</t>
+  </si>
+  <si>
     <t>Empresa</t>
   </si>
   <si>
@@ -82,10 +91,13 @@
     <t>Créditos</t>
   </si>
   <si>
-    <t>Capital pendiente (confirmado)</t>
-  </si>
-  <si>
-    <t>Sin desglose pendiente</t>
+    <t>Capital pendiente confirmado</t>
+  </si>
+  <si>
+    <t>Sin desglose (capital no determinable)</t>
+  </si>
+  <si>
+    <t>Por conciliar (no confirmado)</t>
   </si>
   <si>
     <t>Intereses pendientes</t>
@@ -94,30 +106,36 @@
     <t>Cargos pendientes</t>
   </si>
   <si>
-    <t>Pendiente total</t>
+    <t>Pendiente total confirmado (capital + sin desglose + intereses + cargos)</t>
   </si>
   <si>
     <t>Vencido</t>
   </si>
   <si>
-    <t>Por conciliar (no confirmado)</t>
-  </si>
-  <si>
     <t>Pagado al corte</t>
   </si>
   <si>
-    <t>Capital pendiente USD</t>
+    <t>Capital confirmado USD</t>
+  </si>
+  <si>
+    <t>Sin desglose USD</t>
   </si>
   <si>
     <t>Por conciliar USD</t>
   </si>
   <si>
+    <t>Advertencias (información incompleta)</t>
+  </si>
+  <si>
     <t>Sin resultados para los filtros elegidos.</t>
   </si>
   <si>
     <t>Detalle de créditos · generado 13-10-2026 (ejemplo)</t>
   </si>
   <si>
+    <t>Créditos · saldos al corte de todo el crédito (cartera al corte)</t>
+  </si>
+  <si>
     <t>ID crédito</t>
   </si>
   <si>
@@ -136,48 +154,54 @@
     <t>Vencimiento final</t>
   </si>
   <si>
+    <t>Determinación del capital</t>
+  </si>
+  <si>
+    <t>Pendiente total confirmado</t>
+  </si>
+  <si>
+    <t>Pagos al corte</t>
+  </si>
+  <si>
+    <t>Cuotas en rango</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>TC al corte (unidades por 1 US$)</t>
+  </si>
+  <si>
+    <t>Advertencias</t>
+  </si>
+  <si>
+    <t>Detalle de cuotas (por vencimiento) y pagos registrados (por fecha efectiva) · generado 13-10-2026 (ejemplo)</t>
+  </si>
+  <si>
+    <t>Cuotas · movimientos listados (solo filas del rango); estado al corte</t>
+  </si>
+  <si>
+    <t>ID cuota</t>
+  </si>
+  <si>
+    <t>Vencimiento</t>
+  </si>
+  <si>
+    <t>Origen</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>Interés</t>
+  </si>
+  <si>
+    <t>Cargos</t>
+  </si>
+  <si>
     <t>Sin desglose</t>
   </si>
   <si>
-    <t>Por conciliar</t>
-  </si>
-  <si>
-    <t>Pagos al corte</t>
-  </si>
-  <si>
-    <t>Cuotas en rango</t>
-  </si>
-  <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>TC (moneda por US$)</t>
-  </si>
-  <si>
-    <t>Detalle de cuotas (por vencimiento) y pagos registrados (por fecha efectiva) · generado 13-10-2026 (ejemplo)</t>
-  </si>
-  <si>
-    <t>Cuotas</t>
-  </si>
-  <si>
-    <t>ID cuota</t>
-  </si>
-  <si>
-    <t>Vencimiento</t>
-  </si>
-  <si>
-    <t>Origen</t>
-  </si>
-  <si>
-    <t>Capital</t>
-  </si>
-  <si>
-    <t>Interés</t>
-  </si>
-  <si>
-    <t>Cargos</t>
-  </si>
-  <si>
     <t>Total cuota</t>
   </si>
   <si>
@@ -187,7 +211,7 @@
     <t>Estado al corte</t>
   </si>
   <si>
-    <t>Pagos registrados</t>
+    <t>Pagos registrados · movimientos listados (solo filas del rango)</t>
   </si>
   <si>
     <t>ID pago</t>
@@ -233,6 +257,11 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF0F766E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
@@ -240,13 +269,8 @@
       <i/>
       <sz val="9"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FF0F766E"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +280,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
       </patternFill>
     </fill>
   </fills>
@@ -280,17 +309,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -766,14 +798,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="14" width="16" customWidth="1"/>
+    <col min="5" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
@@ -786,7 +819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="6" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="6" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -801,6 +834,8 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -855,64 +890,83 @@
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="6" t="s">
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="E15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="F15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="G15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="H15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="I15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="J15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="K15" s="7" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="L15" s="7" t="s">
         <v>31</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +984,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -941,10 +995,13 @@
     <col min="6" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="10" width="11" customWidth="1"/>
-    <col min="11" max="17" width="16" customWidth="1"/>
-    <col min="18" max="19" width="8" customWidth="1"/>
-    <col min="20" max="21" width="22" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="11" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="18" width="16" customWidth="1"/>
+    <col min="19" max="20" width="8" customWidth="1"/>
+    <col min="21" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
@@ -954,10 +1011,10 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -980,6 +1037,8 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -1034,88 +1093,107 @@
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="6" t="s">
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="W15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="S13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="T13" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="U13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="V13" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1211,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -1150,7 +1228,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1223,126 +1301,134 @@
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="C15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="G15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>31</v>
       </c>
+      <c r="N15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="J18" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M17" s="6" t="s">
+      <c r="K18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="L18" s="7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>31</v>
+      <c r="M18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
